--- a/product_upload/packages/17/file.xlsx
+++ b/product_upload/packages/17/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -840,6 +845,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>ARIMIDEX 1MG TAB</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-9033572B058D</t>
         </is>
       </c>
@@ -863,7 +873,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1034,6 +1044,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>ARENA 300MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-18EB56BFF169</t>
         </is>
       </c>
@@ -1057,7 +1072,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1228,6 +1243,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>ARENA 150MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-4801B3D56909</t>
         </is>
       </c>
@@ -1251,7 +1271,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1418,6 +1438,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>ARBITEN PLUS</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-B27026CDBEB4</t>
         </is>
       </c>
@@ -1441,7 +1466,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1608,6 +1633,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>ASACOL 400MG F.C TAB</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-648A82594224</t>
         </is>
       </c>
@@ -1631,7 +1661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1794,6 +1824,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>ARBITEN PLUS</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-C2BC0948D311</t>
         </is>
       </c>
@@ -1817,7 +1852,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1980,6 +2015,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>ARBITEN 80MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-6073B03E68EC</t>
         </is>
       </c>
@@ -2003,7 +2043,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2166,6 +2206,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>ARBITEN 160MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-5773B12459EF</t>
         </is>
       </c>
@@ -2189,7 +2234,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2356,6 +2401,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>ARAVA 20MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-3699B082027F</t>
         </is>
       </c>
@@ -2379,7 +2429,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2546,6 +2596,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>ARAVA 10MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-1D4361171A32</t>
         </is>
       </c>
@@ -2569,7 +2624,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KOREA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2734,6 +2789,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>ARAPENTA Injection*</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-EA5AB0A74571</t>
         </is>
       </c>
@@ -2757,7 +2817,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2920,6 +2980,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>ARBITEN PLUS</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-C8B3B337390A</t>
         </is>
       </c>
@@ -2943,7 +3008,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3110,6 +3175,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>ACRETIN</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-95A53B46A885</t>
         </is>
       </c>
@@ -3133,7 +3203,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3296,6 +3366,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>ACRETIN</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-93796FFA5DE3</t>
         </is>
       </c>
@@ -3319,7 +3394,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3486,6 +3561,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>ACNEZOYL 5% GEL</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-2A1F000E8F24</t>
         </is>
       </c>
@@ -3509,7 +3589,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3672,6 +3752,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>ACNELIN</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-1763DDA3C180</t>
         </is>
       </c>
@@ -3695,7 +3780,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3862,6 +3947,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>ACILOC</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-942220F68E62</t>
         </is>
       </c>
@@ -3885,7 +3975,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4040,6 +4130,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>ACILOC</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-91ABBFD87647</t>
         </is>
       </c>
@@ -4063,7 +4158,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4234,6 +4329,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>ACILOC</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-B0F828F4A7C5</t>
         </is>
       </c>
@@ -4257,7 +4357,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4430,6 +4530,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>ADALAT 30MG LA TAB</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-E37FEF31135D</t>
         </is>
       </c>
@@ -4453,7 +4558,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4624,6 +4729,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>ACTRAPID PENFILL</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-8056C0E4964C</t>
         </is>
       </c>
@@ -4647,7 +4757,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4826,6 +4936,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>ACTRAPID</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-B35F673D0995</t>
         </is>
       </c>
@@ -4849,7 +4964,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5016,6 +5131,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>ACTOS 30MG TAB</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-B3D6F3971169</t>
         </is>
       </c>
@@ -5039,7 +5159,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5206,6 +5326,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>ACTOS 15MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-4409D34C9218</t>
         </is>
       </c>
@@ -5229,7 +5354,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5392,6 +5517,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>ACULAR LS 0.4% OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-57B8057E3B8B</t>
         </is>
       </c>
@@ -5415,7 +5545,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5574,6 +5704,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>ADOLIN 0.1% W-W CREAM</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-4BE3FCDF883E</t>
         </is>
       </c>
@@ -5597,7 +5732,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5760,6 +5895,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>ACILOC</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-65D70930D9C6</t>
         </is>
       </c>
@@ -5783,7 +5923,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5954,6 +6094,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>ACILOC</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-A88FCDC83D79</t>
         </is>
       </c>
@@ -5977,7 +6122,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6152,6 +6297,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>ACC LONG 600MG EFFERVESCENT TABLETS</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-12C954053D3C</t>
         </is>
       </c>
@@ -6175,7 +6325,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6346,6 +6496,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>ACC 200MG POWDER FOR ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-F1BBC53F1356</t>
         </is>
       </c>
@@ -6369,7 +6524,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6540,6 +6695,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>ACETAB 25 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-821E68489D8D</t>
         </is>
       </c>
@@ -6563,7 +6723,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6734,6 +6894,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>ACETAB 50 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-92C7D5D5A48E</t>
         </is>
       </c>
@@ -6757,7 +6922,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6920,6 +7085,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>ACID CONC. HAEMODIALYSIS KSP-05 (1+44)</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-72C0F3037956</t>
         </is>
       </c>
@@ -6943,7 +7113,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7106,6 +7276,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>ACILOC</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-519DDC82AC82</t>
         </is>
       </c>
@@ -7129,7 +7304,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7292,6 +7467,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>ACICONE 720 MG CHEWABLE TAB</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-86155AED7AB6</t>
         </is>
       </c>
@@ -7315,7 +7495,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7474,6 +7654,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>ACICONE - S 720 MG CHEWABLE TAB</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-26FA2E10A697</t>
         </is>
       </c>
@@ -7497,7 +7682,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7660,6 +7845,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>ACICONE - S 540MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-5EDFE86F4B69</t>
         </is>
       </c>
@@ -7683,7 +7873,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7846,6 +8036,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>ACICAL PLUS CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-03E031DF683B</t>
         </is>
       </c>
@@ -7869,7 +8064,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8036,6 +8231,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>ACICONE 540MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-24115499760B</t>
         </is>
       </c>
@@ -8059,7 +8259,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8226,6 +8426,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>ADOLIN 0.1% W-W GEL</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-89DD06286055</t>
         </is>
       </c>
@@ -8249,7 +8454,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8420,6 +8625,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>ALKA-UR EFFERVES. 4GM GRANULES SUGARFREE</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-1E70ADD0D4D8</t>
         </is>
       </c>
@@ -8443,7 +8653,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8606,6 +8816,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>ALKA-UR EFFERVES. 4GM GRANULES SUGARFREE</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-ABAF76035D96</t>
         </is>
       </c>
@@ -8629,7 +8844,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8796,6 +9011,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>ALKA-SELTZER</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-654A02269C16</t>
         </is>
       </c>
@@ -8819,7 +9039,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8980,6 +9200,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>ALGEX BALSAM</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-BE3EABE353E2</t>
         </is>
       </c>
@@ -9003,7 +9228,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9162,6 +9387,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>ALGESAL BAUME CREAM</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-05D4D11ECD06</t>
         </is>
       </c>
@@ -9185,7 +9415,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9344,6 +9574,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>ALGESAL BAUME</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-A503E670AC31</t>
         </is>
       </c>
@@ -9367,7 +9602,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9534,6 +9769,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>ALLERFIN TABLETS 4MG</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-10885898421A</t>
         </is>
       </c>
@@ -9557,7 +9797,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9724,6 +9964,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>ALLERGETIN SYRUP</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-5B2C019382CF</t>
         </is>
       </c>
@@ -9747,7 +9992,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9910,6 +10155,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>ALLERGODIL NASAL SPRAY WITH SPRAYER</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-B13D1E890876</t>
         </is>
       </c>
@@ -9933,7 +10183,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10100,6 +10350,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>AMBOLAR</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-C1B2E18CFC58</t>
         </is>
       </c>
@@ -10123,7 +10378,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10292,6 +10547,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>AMARYL 3MG TAB</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-DC90488C2495</t>
         </is>
       </c>
@@ -10315,7 +10575,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10488,6 +10748,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>AMARYL 2MG TAB</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-1E00DB8A91FD</t>
         </is>
       </c>
@@ -10511,7 +10776,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10670,6 +10935,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>ALENDRONATE SANDOZ 70MG F/C TABLET</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-0337D5399C77</t>
         </is>
       </c>
@@ -10693,7 +10963,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10862,6 +11132,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>AMARYL 1MG TAB</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-7589A583C15A</t>
         </is>
       </c>
@@ -10885,7 +11160,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11040,6 +11315,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>ALVESCO 160MCG-PUFF INHALER</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-069C50A2368F</t>
         </is>
       </c>
@@ -11063,7 +11343,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11218,6 +11498,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>ALVESCO 160MCG-PUFF INHALER</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-FC2435E994F9</t>
         </is>
       </c>
@@ -11241,7 +11526,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11410,6 +11695,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>ALPHAGAN-P 0.15% OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-4328701A0AE4</t>
         </is>
       </c>
@@ -11433,7 +11723,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11596,6 +11886,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>ALVESCO 80MCG-PUFF INHALER</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-52A76470B7F4</t>
         </is>
       </c>
@@ -11619,7 +11914,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11782,6 +12077,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>ADRENALINE 1:1000 INJ</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-1A971A2B1EA0</t>
         </is>
       </c>
@@ -11805,7 +12105,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11972,6 +12272,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>ALENDRO</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-C4714B543492</t>
         </is>
       </c>
@@ -11995,7 +12300,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12168,6 +12473,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>ALDOMET 250MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-0DFB57F7CAFC</t>
         </is>
       </c>
@@ -12191,7 +12501,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12362,6 +12672,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>AERIUS 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-CA6E28848ECD</t>
         </is>
       </c>
@@ -12385,7 +12700,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12548,6 +12863,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>AERIUS 2.5 MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-BDD88DDF9CC5</t>
         </is>
       </c>
@@ -12571,7 +12891,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12746,6 +13066,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>ADVIL COLD AND SINUS CAPLET</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-098B0C5495F2</t>
         </is>
       </c>
@@ -12769,7 +13094,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12928,6 +13253,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>ADVIL COLD AND SINUS CAPLET</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-CA9C096ABC42</t>
         </is>
       </c>
@@ -12951,7 +13281,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13124,6 +13454,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>ADVAGRAF 5MG PROLONGED RELEASE CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-9460C307D06C</t>
         </is>
       </c>
@@ -13147,7 +13482,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13316,6 +13651,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>ADVAGRAF 3MG PROLONGED RELEASE CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-5ADB2760E324</t>
         </is>
       </c>
@@ -13339,7 +13679,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13508,6 +13848,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>ADVAGRAF 1MG PROLONGED RELEASE CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-BAA77E0AE577</t>
         </is>
       </c>
@@ -13531,7 +13876,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13700,6 +14045,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>ADVAGRAF 0.5MG PROLONGED RELEASE CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-09FF4AC4FAFD</t>
         </is>
       </c>
@@ -13723,7 +14073,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13890,6 +14240,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>AGIOLAX GRANULES</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-707B00CEC097</t>
         </is>
       </c>
@@ -13913,7 +14268,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14076,6 +14431,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>AGOUT 120 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-FC1091C36D60</t>
         </is>
       </c>
@@ -14099,7 +14459,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14262,6 +14622,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>ALDARA 5% CREAM</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-91C963D75640</t>
         </is>
       </c>
@@ -14285,7 +14650,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14456,6 +14821,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>ALBOTHYL VAGINAL OVULE 90MG</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-007FD6E8146D</t>
         </is>
       </c>
@@ -14479,7 +14849,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14650,6 +15020,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>AIRFAST 4MG GRANULES</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-D820DD7BD47A</t>
         </is>
       </c>
@@ -14673,7 +15048,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14836,6 +15211,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>AIRFAST 4MG CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-2C657667A30F</t>
         </is>
       </c>
@@ -14859,7 +15239,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15030,6 +15410,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>AIRFAST 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-5E611C8652CB</t>
         </is>
       </c>
@@ -15053,7 +15438,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15220,6 +15605,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>AGOUT 80 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-F478CDA8E5D5</t>
         </is>
       </c>
@@ -15243,7 +15633,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15412,6 +15802,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>AGOUT 40 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-8F440AC15AC8</t>
         </is>
       </c>
@@ -15435,7 +15830,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15602,6 +15997,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>AIRFAST 5MG CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-8DA979350307</t>
         </is>
       </c>
@@ -15625,7 +16025,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15792,6 +16192,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>BRIMO-P OPHTHALMIC SOLUTION 0.1%</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-769A814B4307</t>
         </is>
       </c>
@@ -15815,7 +16220,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15986,6 +16391,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>BRIMO</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-B5A30E24B6A6</t>
         </is>
       </c>
@@ -16009,7 +16419,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16182,6 +16592,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>BRILINTA 90 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-3EC522198BA1</t>
         </is>
       </c>
@@ -16205,7 +16620,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16372,6 +16787,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>BONVIVA 150 MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-93DEE9E2C00A</t>
         </is>
       </c>
@@ -16395,7 +16815,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16554,6 +16974,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>BRONCLYN 1.5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-597E64AAE715</t>
         </is>
       </c>
@@ -16577,7 +17002,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16748,6 +17173,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>BRUFEN 400 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-08710E1D442E</t>
         </is>
       </c>
@@ -16771,7 +17201,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16942,6 +17372,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>BRUFEN TAB 600MG</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-9A853F02A401</t>
         </is>
       </c>
@@ -16965,7 +17400,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17134,6 +17569,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>CADUET 10-40</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-8E1000A9325F</t>
         </is>
       </c>
@@ -17157,7 +17597,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17326,6 +17766,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>CADUET 10-20</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-5606F61876E9</t>
         </is>
       </c>
@@ -17349,7 +17794,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17518,6 +17963,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>CADUET 10-10</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-724CB9D078AE</t>
         </is>
       </c>
@@ -17541,7 +17991,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17708,6 +18158,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>BUDIAIR 200 MCG PRESSURISED INH SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-8767D5984F11</t>
         </is>
       </c>
@@ -17731,7 +18186,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17904,6 +18359,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>CADUET 5-10</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-136DC9DDC032</t>
         </is>
       </c>
@@ -17927,7 +18387,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18094,6 +18554,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>BLOPRESS 8 PLUS TABLETS</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-8C6FB8D37AD5</t>
         </is>
       </c>
@@ -18117,7 +18582,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18272,6 +18737,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>BILICANTE 200MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-5BF146C96F17</t>
         </is>
       </c>
@@ -18295,7 +18765,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18466,6 +18936,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>BILAXTEN 20MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-4F8817E2B12A</t>
         </is>
       </c>
@@ -18489,7 +18964,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18666,6 +19141,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>BI PRETERAX ARGININE 5MG-1.25MG F.C. TAB</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-42ED958EAC34</t>
         </is>
       </c>
@@ -18689,7 +19169,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18852,6 +19332,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>BEVASON 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-978086A974E8</t>
         </is>
       </c>
@@ -18875,7 +19360,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19034,6 +19519,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>BEVASON 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-8EEEDA6C6C78</t>
         </is>
       </c>
@@ -19057,7 +19547,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19216,6 +19706,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>BEVACOL 135MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-8356B7968919</t>
         </is>
       </c>
@@ -19239,7 +19734,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19394,6 +19889,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>BETNOVATE-N OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-857B3E52121C</t>
         </is>
       </c>
@@ -19417,7 +19917,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19583,6 +20083,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>BETNOVATE-N 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-62ABD1957C82</t>
         </is>
@@ -19599,7 +20104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19645,100 +20150,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19770,7 +20280,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19785,92 +20295,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-26847</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>419.39</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>85</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19902,7 +20417,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19917,92 +20432,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-90722</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>35.09</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>86</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20034,7 +20554,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20049,92 +20569,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-41407</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>24.53</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>87</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20166,7 +20691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20181,92 +20706,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-42254</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>29.22</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>88</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20298,7 +20828,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20313,92 +20843,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-90621</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>324.65</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>89</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20430,7 +20965,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20445,92 +20980,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-41499</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>429.18</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>90</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20562,7 +21102,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20577,92 +21117,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-46545</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>491.82</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>91</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20694,7 +21239,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20709,92 +21254,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-28179</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>300.94</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>92</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20826,7 +21376,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20841,92 +21391,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-22447</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>120.36</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>93</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20958,7 +21513,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20973,92 +21528,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-62665</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>230.12</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>94</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21090,7 +21650,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21105,92 +21665,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-39771</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>420.83</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>95</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21222,7 +21787,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21237,92 +21802,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-23504</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>157.57</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>96</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21339,7 +21909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21445,6 +22015,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21480,7 +22060,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21545,6 +22125,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-C9DD8E4DC0F4</t>
         </is>
@@ -21581,7 +22171,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21646,6 +22236,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-006CAC44CF39</t>
         </is>
@@ -21682,7 +22282,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21747,6 +22347,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-5C91AC804A19</t>
         </is>
@@ -21783,7 +22393,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21848,6 +22458,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-A544C973158B</t>
         </is>
@@ -21884,7 +22504,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21949,6 +22569,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-EDE7856C5A78</t>
         </is>
@@ -21985,7 +22615,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22050,6 +22680,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-ADCEB448780A</t>
         </is>
@@ -22086,7 +22726,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22151,6 +22791,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-663BF4413DA1</t>
         </is>
@@ -22187,7 +22837,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22252,6 +22902,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-01C7754AF747</t>
         </is>
@@ -22288,7 +22948,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22353,6 +23013,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-60551A419815</t>
         </is>
@@ -22389,7 +23059,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22454,6 +23124,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-6538E976CD22</t>
         </is>
@@ -22490,7 +23170,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22555,6 +23235,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-6C947865A433</t>
         </is>
@@ -22591,7 +23281,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22656,6 +23346,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-978FE7686346</t>
         </is>
@@ -22692,7 +23392,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22757,6 +23457,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-CA5F992D4A2F</t>
         </is>
@@ -22793,7 +23503,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22858,6 +23568,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-B07ADF444FCE</t>
         </is>
@@ -22894,7 +23614,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22959,6 +23679,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-7853A0FD1AB0</t>
         </is>
@@ -22995,7 +23725,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23060,6 +23790,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-C1596D76DEF8</t>
         </is>
@@ -23096,7 +23836,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23161,6 +23901,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-DC5EA7CDC5EE</t>
         </is>
@@ -23197,7 +23947,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23262,6 +24012,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-B67DF45EB797</t>
         </is>
@@ -23298,7 +24058,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23363,6 +24123,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-40CF0323C249</t>
         </is>
@@ -23399,7 +24169,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23464,6 +24234,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-23084EB8CDDD</t>
         </is>

--- a/product_upload/packages/17/file.xlsx
+++ b/product_upload/packages/17/file.xlsx
@@ -1279,8 +1279,16 @@
           <t>9981399781-252-439329523808</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBITEN PLUS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ARBITEN PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1669,8 +1677,16 @@
           <t>1685510772-237-856737660738</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBITEN PLUS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ARBITEN PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1860,8 +1876,16 @@
           <t>9522205379-328-711688916781</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBITEN 80MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ARBITEN 80MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2051,8 +2075,16 @@
           <t>6874765558-517-894361306898</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBITEN 160MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ARBITEN 160MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2632,8 +2664,16 @@
           <t>5632288075-524-932994204360</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARAPENTA Injection*</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ARAPENTA Injection* detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>ARAB COMPANY FOR PHARMACEUTICAL PRODUCTS (ARABIO)</t>
@@ -2825,8 +2865,16 @@
           <t>7290641913-860-356538927347</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARBITEN PLUS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ARBITEN PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3597,8 +3645,16 @@
           <t>4431757232-236-561597924403</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACNELIN</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ACNELIN detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3983,8 +4039,16 @@
           <t>0194282773-833-285585700725</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACILOC</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ACILOC detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4566,8 +4630,16 @@
           <t>9726848903-034-420104933188</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACTRAPID PENFILL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ACTRAPID PENFILL detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -5553,8 +5625,16 @@
           <t>8568823612-078-293246991549</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADOLIN 0.1% W-W CREAM</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ADOLIN 0.1% W-W CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -6930,8 +7010,16 @@
           <t>1684163958-079-699073591365</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACID CONC. HAEMODIALYSIS KSP-05 (1+44)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ACID CONC. HAEMODIALYSIS KSP-05 (1+44) detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7121,8 +7209,16 @@
           <t>7952631887-386-828566241065</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACILOC</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ACILOC detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7312,8 +7408,16 @@
           <t>5106553640-890-480741960847</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACICONE 720 MG CHEWABLE TAB</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ACICONE 720 MG CHEWABLE TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7503,8 +7607,16 @@
           <t>3959329690-677-602433797872</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACICONE - S 720 MG CHEWABLE TAB</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ACICONE - S 720 MG CHEWABLE TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7690,8 +7802,16 @@
           <t>7959784206-360-392993307911</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACICONE - S 540MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ACICONE - S 540MG-5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -8072,8 +8192,16 @@
           <t>7192093181-226-782695098569</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ACICONE 540MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ACICONE 540MG-5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8852,8 +8980,16 @@
           <t>6850114747-219-901800751120</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALKA-SELTZER</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ALKA-SELTZER detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -9047,8 +9183,16 @@
           <t>5762009106-095-878839084719</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALGEX BALSAM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ALGEX BALSAM detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9236,8 +9380,16 @@
           <t>1178484222-337-729617069063</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALGESAL BAUME CREAM</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ALGESAL BAUME CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9423,8 +9575,16 @@
           <t>2487840921-887-815920835102</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALGESAL BAUME</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ALGESAL BAUME detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9805,8 +9965,16 @@
           <t>5211092859-206-986898512134</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALLERGETIN SYRUP</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ALLERGETIN SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -10000,8 +10168,16 @@
           <t>2625487251-828-831217043023</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALLERGODIL NASAL SPRAY WITH SPRAYER</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ALLERGODIL NASAL SPRAY WITH SPRAYER detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10784,8 +10960,16 @@
           <t>8657637155-832-563710123526</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALENDRONATE SANDOZ 70MG F/C TABLET</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ALENDRONATE SANDOZ 70MG F/C TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -11168,8 +11352,16 @@
           <t>4907920855-290-928243330587</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALVESCO 160MCG-PUFF INHALER</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ALVESCO 160MCG-PUFF INHALER detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11351,8 +11543,16 @@
           <t>1221709293-828-281144271491</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALVESCO 160MCG-PUFF INHALER</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ALVESCO 160MCG-PUFF INHALER detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11731,8 +11931,16 @@
           <t>4906538404-012-180918856152</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALVESCO 80MCG-PUFF INHALER</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>ALVESCO 80MCG-PUFF INHALER detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11922,8 +12130,16 @@
           <t>0232472582-845-104207678584</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADRENALINE 1:1000 INJ</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ADRENALINE 1:1000 INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -13102,8 +13318,16 @@
           <t>4709011644-902-657287383951</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADVIL COLD AND SINUS CAPLET</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ADVIL COLD AND SINUS CAPLET detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -14276,8 +14500,16 @@
           <t>5955391279-304-430919710971</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AGOUT 120 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>AGOUT 120 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14467,8 +14699,16 @@
           <t>2962188356-995-716347423001</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALDARA 5% CREAM</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ALDARA 5% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -16628,8 +16868,16 @@
           <t>4982988784-145-740449405022</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BONVIVA 150 MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>BONVIVA 150 MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16823,8 +17071,16 @@
           <t>8971329381-851-497356196252</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRONCLYN 1.5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>BRONCLYN 1.5MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -18590,8 +18846,16 @@
           <t>5394980745-368-857084867639</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BILICANTE 200MG CAPS</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>BILICANTE 200MG CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -19177,8 +19441,16 @@
           <t>8308886734-813-208209667353</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BEVASON 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>BEVASON 0.1% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19368,8 +19640,16 @@
           <t>5948563807-501-271122795628</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BEVASON 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>BEVASON 0.1% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19555,8 +19835,16 @@
           <t>1299637456-350-977443547960</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BEVACOL 135MG TABLET</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>BEVACOL 135MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19742,8 +20030,16 @@
           <t>2170284509-498-504296744075</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETNOVATE-N OINTMENT</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>BETNOVATE-N OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/17/file.xlsx
+++ b/product_upload/packages/17/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20446,7 +20446,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22205,7 +22205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22286,40 +22286,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22399,38 +22404,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>81.97</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-C9DD8E4DC0F4</t>
         </is>
@@ -22510,38 +22520,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>373.35</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-006CAC44CF39</t>
         </is>
@@ -22621,38 +22636,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>224.48</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-5C91AC804A19</t>
         </is>
@@ -22732,38 +22752,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>229.84</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-A544C973158B</t>
         </is>
@@ -22843,38 +22868,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>311.14</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-EDE7856C5A78</t>
         </is>
@@ -22954,38 +22984,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>373.5</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-ADCEB448780A</t>
         </is>
@@ -23065,38 +23100,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>458.44</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-663BF4413DA1</t>
         </is>
@@ -23176,38 +23216,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>371.99</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-01C7754AF747</t>
         </is>
@@ -23287,38 +23332,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>399.4</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-60551A419815</t>
         </is>
@@ -23398,38 +23448,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>310.84</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-6538E976CD22</t>
         </is>
@@ -23509,38 +23564,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>342.58</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-6C947865A433</t>
         </is>
@@ -23620,38 +23680,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>295.98</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-978FE7686346</t>
         </is>
@@ -23731,38 +23796,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>163.6</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-CA5F992D4A2F</t>
         </is>
@@ -23842,38 +23912,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>445.29</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-B07ADF444FCE</t>
         </is>
@@ -23953,38 +24028,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>355.96</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-7853A0FD1AB0</t>
         </is>
@@ -24064,38 +24144,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>425.56</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-C1596D76DEF8</t>
         </is>
@@ -24175,38 +24260,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>84.3</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-DC5EA7CDC5EE</t>
         </is>
@@ -24286,38 +24376,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>34.19</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-B67DF45EB797</t>
         </is>
@@ -24397,38 +24492,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>420.13</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-40CF0323C249</t>
         </is>
@@ -24508,38 +24608,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>426.48</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-23084EB8CDDD</t>
         </is>
